--- a/ADMA_CAIQ_v4.0.3_Completed_2026-08-28.xlsx
+++ b/ADMA_CAIQ_v4.0.3_Completed_2026-08-28.xlsx
@@ -1293,7 +1293,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>The app runs on a single EC2 instance with no documented BCP/DR plan, no failover/redundancy, and no tested recovery procedure. UPDATE 2026-08-05: DISASTER_RECOVERY_PLAN.md is a real, documented, applied BC plan.</t>
+          <t>The app runs on a single EC2 instance with no documented BCP/DR plan, no failover/redundancy, and no tested recovery procedure. UPDATE 2026-08-05: DISASTER_RECOVERY_PLAN.md is a real, documented, applied BC plan. UPDATE 2026-08-28 (b): “no failover/redundancy” is now stale — a live warm-standby instance in a different AZ exists (PROMOTION_RUNBOOK.md, verified reachable/healthy end-to-end since 2026-08-06), promoted manually rather than automatically.</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>The app runs on a single EC2 instance with no documented BCP/DR plan, no failover/redundancy, and no tested recovery procedure. UPDATE 2026-08-05: DISASTER_RECOVERY_PLAN.md's RTO/RPO reasoning is tied to real disruption/risk-impact scenarios.</t>
+          <t>The app runs on a single EC2 instance with no documented BCP/DR plan, no failover/redundancy, and no tested recovery procedure. UPDATE 2026-08-05: DISASTER_RECOVERY_PLAN.md's RTO/RPO reasoning is tied to real disruption/risk-impact scenarios. UPDATE 2026-08-28 (b): same correction as BCR-01.1 — the warm-standby's existence is itself evidence the resiliency strategy accounts for real disruption scenarios (single-instance/single-AZ failure), not just a paper plan.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>No documented DR/BCP plan; the app runs on a single EC2 instance with no failover — an instance or AZ failure would cause an outage with no automatic recovery path. UPDATE 2026-08-05: incorporated into DISASTER_RECOVERY_PLAN.md.</t>
+          <t>No documented DR/BCP plan; the app runs on a single EC2 instance with no failover — an instance or AZ failure would cause an outage with no automatic recovery path. UPDATE 2026-08-05: incorporated into DISASTER_RECOVERY_PLAN.md. UPDATE 2026-08-28 (b): “no failover” is now stale — a live, verified-reachable warm standby exists; “no automatic recovery path” remains accurate (promotion is a manual runbook, not automatic).</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>The app runs on a single EC2 instance with no documented BCP/DR plan, no failover/redundancy, and no tested recovery procedure. UPDATE 2026-08-05: one real restore was tested end-to-end (adma_app_settings -&gt; scratch table -&gt; verified -&gt; deleted), but this is a single exercise, not an established annual test cycle for the full BC plan.</t>
+          <t>The app runs on a single EC2 instance with no documented BCP/DR plan, no failover/redundancy, and no tested recovery procedure. UPDATE 2026-08-05: one real restore was tested end-to-end (adma_app_settings -&gt; scratch table -&gt; verified -&gt; deleted), but this is a single exercise, not an established annual test cycle for the full BC plan. UPDATE 2026-08-28 (b): a second real exercise beyond the DynamoDB restore test — the warm standby's reachability was independently verified end-to-end (2026-08-06) — still short of an established annual full-BC-plan test cycle.</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>The app runs on a single EC2 instance with no documented BCP/DR plan, no failover/redundancy, and no tested recovery procedure. UPDATE 2026-08-05: INCIDENT_RESPONSE_PLAN.md Section 3 establishes stakeholder communication (72h notification commitment).</t>
+          <t>The app runs on a single EC2 instance with no documented BCP/DR plan, no failover/redundancy, and no tested recovery procedure. UPDATE 2026-08-05: INCIDENT_RESPONSE_PLAN.md Section 3 establishes stakeholder communication (72h notification commitment). UPDATE 2026-08-28 (b): “no failover/redundancy” is now stale (see BCR-01.1); the real evidence for this specific question remains INCIDENT_RESPONSE_PLAN.md §3's stakeholder communication commitment.</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>The app runs on a single EC2 instance with no documented BCP/DR plan, no failover/redundancy, and no tested recovery procedure. UPDATE 2026-08-05: one real restore exercise was performed (see BCR-06.1) but not a full annual DR-plan exercise cycle.</t>
+          <t>The app runs on a single EC2 instance with no documented BCP/DR plan, no failover/redundancy, and no tested recovery procedure. UPDATE 2026-08-05: one real restore exercise was performed (see BCR-06.1) but not a full annual DR-plan exercise cycle. UPDATE 2026-08-28 (b): same second exercise as BCR-06.1 (warm-standby reachability verified end-to-end) — still not a full annual DR-plan exercise cycle.</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow.</t>
+          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow. UPDATE 2026-08-28 (b): DATA_CLASSIFICATION_AND_RETENTION.md §3's deletion process (locate, delete/anonymize, confirm) is real, but it's logical deletion via DynamoDB/S3 delete operations — physical-media-level unrecoverability is AWS's own responsibility as the underlying storage provider (SSRM: inherited), not something ADMA verifies independently.</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow.</t>
+          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow. UPDATE 2026-08-28 (b): DATA_CLASSIFICATION_AND_RETENTION.md §1's classification table (category, where it lives, sensitivity, for all 6 data categories) is real, documented ownership/stewardship — short of naming an individual steward per category.</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow.</t>
+          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow. UPDATE 2026-08-28 (b): same evidence already credited to DSP-01.2 — DATA_CLASSIFICATION_AND_RETENTION.md §5 explicitly commits to annual review, and this question asks the identical thing (review cadence) about the identical document, just from the “ownership/stewardship” framing rather than “privacy policy” framing. Consistency fix.</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr"/>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow.</t>
+          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow. UPDATE 2026-08-28 (b): real technical security-by-design practice exists (server/lib/ownership.js's per-record scoping, bcrypt hashing, RBAC — already cited elsewhere in this document) even though there's no separate written “security by design” policy statement naming it as such.</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow.</t>
+          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow. UPDATE 2026-08-28 (b): same technical practice as DSP-07.1 (ownership scoping limits data exposure by default) is privacy-by-design in substance, without a named policy document.</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow.</t>
+          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow. UPDATE 2026-08-28 (b): sensitive fields (password_hash, totp_secret) are never returned by any API by default, and per-record ownership scoping means a user's default view is already limited to their own data — real default-privacy behavior, not configurable-but-defaulted-open.</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow.</t>
+          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow. UPDATE 2026-08-28 (b): the AWS Bedrock addition (2026-08-28) is a direct, current example of exactly this control being applied — VENDOR_DEPENDENCY_REVIEW.md and the Privacy Policy both now disclose that this specific transfer (exhibitor text to us-east-1) is opt-in only, scoped to the stated purpose (draft suggestions), and nothing is retained by the receiving service beyond the request.</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>No automated data-subject deletion/export workflow or documented retention schedule; would be handled manually on request today.</t>
+          <t>No automated data-subject deletion/export workflow or documented retention schedule; would be handled manually on request today. UPDATE 2026-08-28 (b): PrivacyPolicy.jsx §3 explicitly declares the purposes personal data is processed for, and per-record ownership scoping technically prevents processing outside a user's own scope — real evidence of purpose limitation, short of an automated enforcement/audit mechanism confirming no processing ever occurs outside declared purposes.</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow.</t>
+          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow. UPDATE 2026-08-28 (b): DATA_CLASSIFICATION_AND_RETENTION.md's four sections together (classification, retention, deletion, encryption) cover the data lifecycle end to end — same reasoning already applied to DSP-05.1's “Yes.”</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow.</t>
+          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow. UPDATE 2026-08-28 (b): GOVERNANCE_ADDENDUM.md §4 (already cited for SEF-08.1) establishes an internal routing process for law-enforcement/regulatory requests — directly applicable here too, just never cross-referenced from this row.</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow.</t>
+          <t>Server-side ownership scoping limits data access to the correct user/exhibitor, and sensitive fields (password_hash, totp_secret) are stripped from API responses, but there is no formal data classification scheme, documented retention/deletion schedule, or automated data-subject request workflow. UPDATE 2026-08-28 (b): same GOVERNANCE_ADDENDUM.md §4 process as DSP-18.1 covers notification to affected parties where not legally prohibited, though no specific case has ever tested it.</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr"/>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>Structured security-event logging exists (`logSecurityEvent` — logins, MFA failures, admin lock/unlock, CSP violations) but with no defined retention period or scheduled review.</t>
+          <t>Structured security-event logging exists (`logSecurityEvent` — logins, MFA failures, admin lock/unlock, CSP violations) but with no defined retention period or scheduled review. UPDATE 2026-08-28 (b): CLOUDTRAIL_SETUP.md and CLOUDWATCH_LOGGING_SETUP.md are real, documented, approved, and applied logging procedures with stated retention (365 days) — corrects this row's prior claim of “no... AWS CloudTrail,” which has been false since 2026-08-05.</t>
         </is>
       </c>
       <c r="F192" s="8" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Structured JSON security-event logs (logins, MFA failures, CSP violations) are written to stdout and captured by pm2, but there is no centralized log aggregation/SIEM, defined retention policy, alerting, or AWS CloudTrail.</t>
+          <t>Structured JSON security-event logs (logins, MFA failures, CSP violations) are written to stdout and captured by pm2, but there is no centralized log aggregation/SIEM, defined retention policy, alerting, or AWS CloudTrail. UPDATE 2026-08-28 (b): corrects the prior “no... AWS CloudTrail” claim, false since 2026-08-05 (see CLOUDTRAIL_SETUP.md, CLOUDWATCH_LOGGING_SETUP.md) — but neither setup doc commits to an annual policy-review cadence specifically, so this stays genuinely Partial.</t>
         </is>
       </c>
       <c r="F193" s="8" t="inlineStr"/>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>Structured security-event logging exists (`logSecurityEvent` — logins, MFA failures, admin lock/unlock, CSP violations) but with no defined retention period or scheduled review.</t>
+          <t>Structured security-event logging exists (`logSecurityEvent` — logins, MFA failures, admin lock/unlock, CSP violations) but with no defined retention period or scheduled review. UPDATE 2026-08-28 (b): corrects the prior “no... AWS CloudTrail” claim, false since 2026-08-05 — logs are genuinely centralized and retained now, but active anomaly monitoring/alerting still doesn't exist, so the core gap this question is really asking about remains real.</t>
         </is>
       </c>
       <c r="F198" s="8" t="inlineStr">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Structured JSON security-event logs (logins, MFA failures, CSP violations) are written to stdout and captured by pm2, but there is no centralized log aggregation/SIEM, defined retention policy, alerting, or AWS CloudTrail.</t>
+          <t>Structured JSON security-event logs (logins, MFA failures, CSP violations) are written to stdout and captured by pm2, but there is no centralized log aggregation/SIEM, defined retention policy, alerting, or AWS CloudTrail. UPDATE 2026-08-28 (b): corrects the prior “no... AWS CloudTrail” claim, false since 2026-08-05 — the underlying gap (no defined anomaly-review-and-action process) remains genuinely open.</t>
         </is>
       </c>
       <c r="F199" s="8" t="inlineStr"/>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>Structured JSON security-event logs (logins, MFA failures, CSP violations) are written to stdout and captured by pm2, but there is no centralized log aggregation/SIEM, defined retention policy, alerting, or AWS CloudTrail.</t>
+          <t>Structured JSON security-event logs (logins, MFA failures, CSP violations) are written to stdout and captured by pm2, but there is no centralized log aggregation/SIEM, defined retention policy, alerting, or AWS CloudTrail. UPDATE 2026-08-28 (b): AWS EC2 instances and CloudTrail both use AWS's own NTP-synchronized time infrastructure — a reliable time source is inherited from AWS, same SSRM basis as Datacenter Security's 100% score, not something ADMA needs to configure separately.</t>
         </is>
       </c>
       <c r="F200" s="8" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="E202" s="8" t="inlineStr">
         <is>
-          <t>Structured JSON security-event logs (logins, MFA failures, CSP violations) are written to stdout and captured by pm2, but there is no centralized log aggregation/SIEM, defined retention policy, alerting, or AWS CloudTrail.</t>
+          <t>Structured JSON security-event logs (logins, MFA failures, CSP violations) are written to stdout and captured by pm2, but there is no centralized log aggregation/SIEM, defined retention policy, alerting, or AWS CloudTrail. UPDATE 2026-08-28 (b): corrects the prior “no... AWS CloudTrail” claim, false since 2026-08-05 — no explicit annual scope-review commitment exists for the logging configuration specifically, so this stays Partial.</t>
         </is>
       </c>
       <c r="F202" s="8" t="inlineStr"/>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>Structured JSON security-event logs (logins, MFA failures, CSP violations) are written to stdout and captured by pm2, but there is no centralized log aggregation/SIEM, defined retention policy, alerting, or AWS CloudTrail.</t>
+          <t>Structured JSON security-event logs (logins, MFA failures, CSP violations) are written to stdout and captured by pm2, but there is no centralized log aggregation/SIEM, defined retention policy, alerting, or AWS CloudTrail. UPDATE 2026-08-28 (b): corrects the prior “no... AWS CloudTrail” claim — CloudTrail does capture KMS/encryption-related API calls as part of its management-event logging, though there's no dedicated reporting/dashboard surfacing them specifically.</t>
         </is>
       </c>
       <c r="F205" s="8" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="E206" s="8" t="inlineStr">
         <is>
-          <t>Structured security-event logging exists (`logSecurityEvent` — logins, MFA failures, admin lock/unlock, CSP violations) but with no defined retention period or scheduled review.</t>
+          <t>Structured security-event logging exists (`logSecurityEvent` — logins, MFA failures, admin lock/unlock, CSP violations) but with no defined retention period or scheduled review. UPDATE 2026-08-28 (b): corrects the prior “no... AWS CloudTrail” claim — CloudTrail captures key-lifecycle-relevant API events as part of its management-event logging, though (per KEY_MANAGEMENT_POLICY.md's own scope) there are no customer-managed KMS keys with a lifecycle to monitor in the first place.</t>
         </is>
       </c>
       <c r="F206" s="8" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="E208" s="8" t="inlineStr">
         <is>
-          <t>Structured JSON security-event logs (logins, MFA failures, CSP violations) are written to stdout and captured by pm2, but there is no centralized log aggregation/SIEM, defined retention policy, alerting, or AWS CloudTrail.</t>
+          <t>Structured JSON security-event logs (logins, MFA failures, CSP violations) are written to stdout and captured by pm2, but there is no centralized log aggregation/SIEM, defined retention policy, alerting, or AWS CloudTrail. UPDATE 2026-08-28 (b): corrects the prior “no... AWS CloudTrail” claim, false since 2026-08-05 — the real gap (no defined anomaly/failure reporting process beyond log collection itself) remains open.</t>
         </is>
       </c>
       <c r="F208" s="8" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>Structured JSON security-event logs (logins, MFA failures, CSP violations) are written to stdout and captured by pm2, but there is no centralized log aggregation/SIEM, defined retention policy, alerting, or AWS CloudTrail.</t>
+          <t>Structured JSON security-event logs (logins, MFA failures, CSP violations) are written to stdout and captured by pm2, but there is no centralized log aggregation/SIEM, defined retention policy, alerting, or AWS CloudTrail. UPDATE 2026-08-28 (b): corrects the prior “no... AWS CloudTrail” claim — no automated alerting to accountable parties exists yet; this genuinely stays open.</t>
         </is>
       </c>
       <c r="F209" s="8" t="inlineStr"/>
